--- a/data/trans_orig/IQ09_A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 8,37</t>
+          <t>1,24; 8,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 10,93</t>
+          <t>2,62; 10,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,4</t>
+          <t>0,46; 5,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 10,61</t>
+          <t>3,16; 10,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,06</t>
+          <t>1,23; 5,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,52</t>
+          <t>1,55; 5,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,97</t>
+          <t>0,48; 2,92</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,54</t>
+          <t>0,55; 2,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,92</t>
+          <t>1,18; 3,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,02</t>
+          <t>0,58; 3,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,38</t>
+          <t>1,33; 5,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,82</t>
+          <t>1,16; 4,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,35</t>
+          <t>1,49; 4,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,37</t>
+          <t>1,03; 4,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,86</t>
+          <t>3,51; 7,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,6</t>
+          <t>1,23; 3,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,34</t>
+          <t>1,62; 3,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,12</t>
+          <t>1,02; 3,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,17</t>
+          <t>3,09; 6,23</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,67</t>
+          <t>0,99; 8,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,41</t>
+          <t>0,53; 3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,67</t>
+          <t>1,49; 6,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,76</t>
+          <t>0,87; 5,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 10,41</t>
+          <t>0,64; 9,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,66</t>
+          <t>0,76; 5,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,51</t>
+          <t>1,21; 6,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,58</t>
+          <t>1,33; 5,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,5</t>
+          <t>0,41; 6,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,08</t>
+          <t>1,06; 4,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,68</t>
+          <t>1,9; 5,72</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,53</t>
+          <t>1,31; 4,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,17</t>
+          <t>1,35; 3,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,39</t>
+          <t>0,9; 3,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,64</t>
+          <t>1,91; 4,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,16</t>
+          <t>1,98; 4,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,2</t>
+          <t>1,69; 4,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,75</t>
+          <t>1,35; 3,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,91</t>
+          <t>2,88; 5,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,17</t>
+          <t>1,98; 4,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,22</t>
+          <t>1,73; 3,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,94</t>
+          <t>1,37; 2,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,91</t>
+          <t>2,72; 4,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Estudios-trans_orig.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 8,28</t>
+          <t>1,18; 8,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 10,93</t>
+          <t>2,62; 10,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,36</t>
+          <t>0,46; 5,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,47</t>
+          <t>2,98; 10,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,12</t>
+          <t>1,3; 5,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,92</t>
+          <t>0,48; 2,93</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,47</t>
+          <t>0,49; 2,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,18</t>
+          <t>1,24; 3,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,81</t>
+          <t>0,61; 3,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,65</t>
+          <t>1,25; 5,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,64</t>
+          <t>1,24; 4,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,54</t>
+          <t>1,43; 4,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,23</t>
+          <t>1,02; 4,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,71</t>
+          <t>3,49; 7,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,66</t>
+          <t>1,24; 3,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,51</t>
+          <t>1,57; 3,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,14</t>
+          <t>1,06; 3,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,23</t>
+          <t>3,04; 6,2</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,02</t>
+          <t>1,12; 9,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,63</t>
+          <t>0,54; 3,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,58</t>
+          <t>1,42; 6,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,83</t>
+          <t>0,94; 5,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,32 +1026,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,97</t>
+          <t>0,75; 5,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,46</t>
+          <t>0,91; 6,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,28</t>
+          <t>1,47; 5,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,13</t>
+          <t>0,5; 6,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,21</t>
+          <t>1,09; 4,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,72</t>
+          <t>1,91; 5,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,84</t>
+          <t>1,31; 4,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,23</t>
+          <t>1,29; 3,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,2</t>
+          <t>0,92; 3,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,54</t>
+          <t>2,1; 4,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,93</t>
+          <t>1,86; 4,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,15</t>
+          <t>1,63; 4,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,83</t>
+          <t>1,32; 3,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,83</t>
+          <t>2,75; 5,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,18</t>
+          <t>1,97; 4,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,24</t>
+          <t>1,66; 3,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,92</t>
+          <t>1,32; 3,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,82</t>
+          <t>2,79; 4,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,68</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,21</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,76</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2,61; 10,93</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,38; 5,4</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 6,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,9</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1,67; 14,0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 8,09</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,32; 8,37</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2,0; 3,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>1,0; 3,0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,62; 10,98</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 5,82</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,83</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,24</t>
+          <t>3,03; 10,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,6</t>
+          <t>1,26; 5,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,42</t>
+          <t>1,55; 5,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,93</t>
+          <t>0,3; 2,55</t>
         </is>
       </c>
     </row>
@@ -788,49 +788,49 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,55</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,65</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,37</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,39</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,94</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,53</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,99</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3,19</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,21</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2,33</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,46</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,42</t>
+          <t>1,19; 4,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,14</t>
+          <t>1,44; 4,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,91</t>
+          <t>1,06; 4,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,31</t>
+          <t>3,59; 8,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,85</t>
+          <t>0,58; 2,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,28</t>
+          <t>1,19; 2,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,07</t>
+          <t>0,61; 4,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,84</t>
+          <t>1,47; 5,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,65</t>
+          <t>1,24; 3,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,35</t>
+          <t>1,56; 3,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,08</t>
+          <t>1,1; 3,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,2</t>
+          <t>3,01; 6,41</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,88</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,56</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,56</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,55</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,82</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,88</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,56</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>3,98</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>3,77</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,85</t>
+          <t>0,74; 5,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,65; 10,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,66</t>
+          <t>0,78; 5,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,41</t>
+          <t>1,01; 6,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,99</t>
+          <t>1,12; 9,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 9,98</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,9</t>
+          <t>0,55; 3,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 6,4</t>
+          <t>1,49; 6,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,41</t>
+          <t>1,34; 5,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 6,34</t>
+          <t>0,56; 6,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,25</t>
+          <t>1,03; 4,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,64</t>
+          <t>1,86; 5,75</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,67</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,56</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,51</t>
+          <t>1,98; 5,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,15</t>
+          <t>1,67; 4,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,22</t>
+          <t>1,36; 3,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,72</t>
+          <t>2,85; 6,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,79</t>
+          <t>1,3; 4,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,11</t>
+          <t>1,31; 3,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,8</t>
+          <t>1,0; 3,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,9</t>
+          <t>1,88; 5,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,22</t>
+          <t>1,91; 4,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,21</t>
+          <t>1,63; 3,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,0</t>
+          <t>1,29; 2,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,93</t>
+          <t>2,84; 5,34</t>
         </is>
       </c>
     </row>
